--- a/Progress_checking.xlsx
+++ b/Progress_checking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\Code\0_Thesis_implementation\2_DIDP_custom_search_guidance_local\Thesis_modified_DIDP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51058BB-A986-44B0-BD9F-AD3EE71E04D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C841CE-731F-4B3E-BFB2-239A3414B0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1164" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -146,53 +146,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color theme="0"/>
@@ -200,29 +154,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
         </patternFill>
       </fill>
       <border>
@@ -266,84 +197,9 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
       <border>
@@ -752,13 +608,13 @@
         <v>11</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>13</v>
@@ -781,7 +637,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>13</v>
@@ -804,7 +660,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>13</v>
@@ -823,25 +679,14 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:G6">
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
-      <formula>"Done"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+  <conditionalFormatting sqref="B2:H6">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Pending"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"In execution"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H6">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"Pending"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"In execution"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
